--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260820.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260820.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>567,660,452</t>
+          <t>567,762,332</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>57.71%</t>
+          <t>58.11%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>34,200,529</t>
+          <t>34,206,681</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>5.69%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>44,868,633</t>
+          <t>44,876,705</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>3.43%</t>
+          <t>3.37%</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>283,763,431</t>
+          <t>283,814,495</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>77,103,705</t>
+          <t>77,117,577</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,752,667</t>
+          <t>6,753,875</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.74%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>30,652,669</t>
+          <t>30,658,181</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>270,986,741</t>
+          <t>271,035,517</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>411,450,181</t>
+          <t>411,496,421</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>193,950,299</t>
+          <t>193,985,179</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>11,513,048</t>
+          <t>11,515,120</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>7,435,868</t>
+          <t>7,437,204</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>221,756,715</t>
+          <t>221,796,595</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>114,523,276</t>
+          <t>114,543,876</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>36,588,290</t>
+          <t>36,594,874</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -941,12 +941,12 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,463,939</t>
+          <t>61,474,987</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>544,634,532</t>
+          <t>544,732,532</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>8,566,716</t>
+          <t>8,568,252</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>1,281,220</t>
+          <t>1,281,444</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>266,764,498</t>
+          <t>266,812,450</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>2,415,452</t>
+          <t>2,415,884</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.66%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>15,696,233</t>
+          <t>15,699,049</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1095,51 +1095,51 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>371,936,522</t>
+          <t>372,000,098</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>275,008,688</t>
+          <t>26,544,828</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>26,540,060</t>
+          <t>275,058,112</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>70,218,324</t>
+          <t>71,923,096</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>45,495,089</t>
+          <t>70,230,948</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>永豐金</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>71,910,160</t>
+          <t>304,693,100</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中華電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>88,760,414</t>
+          <t>2,186,460</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1239,17 +1239,17 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2890</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>永豐金</t>
+          <t>中華電</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>304,638,324</t>
+          <t>88,776,366</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,17 +1261,17 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,186,068</t>
+          <t>45,503,265</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>2,022,885</t>
+          <t>2,023,245</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>366,234,876</t>
+          <t>366,300,732</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>1,864,342</t>
+          <t>1,864,670</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>4,157,866</t>
+          <t>4,158,610</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>115,093,662</t>
+          <t>115,114,326</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,39 +1393,39 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>260,761,956</t>
+          <t>1,325,380</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.37%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>1,325,148</t>
+          <t>260,808,788</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>216,180,040</t>
+          <t>216,218,864</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,39 +1459,39 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>金像電</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>7,990,482</t>
+          <t>17,729,286</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>2368</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>金像電</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>17,726,102</t>
+          <t>7,991,914</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1513,12 +1513,12 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>10,739,924</t>
+          <t>10,741,852</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>1,838,768</t>
+          <t>1,839,096</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>250,486,772</t>
+          <t>250,531,644</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>26,565,501</t>
+          <t>26,570,269</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>25,435,144</t>
+          <t>25,439,680</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>4,982,682</t>
+          <t>4,983,570</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>41,309,626</t>
+          <t>41,317,042</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>32,987,139</t>
+          <t>32,993,043</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>26,934,735</t>
+          <t>26,939,527</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
